--- a/EffectTable_效果表.xlsx
+++ b/EffectTable_效果表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通用效果" sheetId="1" r:id="R6b0bba84922647da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通用效果" sheetId="1" r:id="R9d91214145854d47"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="2">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -23,8 +23,14 @@
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -34,6 +40,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8EEF4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF403728"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -49,7 +60,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="10">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -63,6 +74,15 @@
         </x:ext>
       </x:extLst>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -286,7 +306,7 @@
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="86" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -315,82 +335,82 @@
       <x:c r="F2" s="1"/>
     </x:row>
     <x:row r="3" ht="44" customHeight="1">
-      <x:c r="A3" s="2" t="str">
+      <x:c r="A3" s="8" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="str">
+      <x:c r="B3" s="8" t="str">
         <x:v>效果类型</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="str">
+      <x:c r="C3" s="8" t="str">
         <x:v>目标</x:v>
       </x:c>
-      <x:c r="D3" s="2" t="str">
+      <x:c r="D3" s="8" t="str">
         <x:v>数值</x:v>
       </x:c>
-      <x:c r="E3" s="2" t="str">
+      <x:c r="E3" s="8" t="str">
         <x:v>说明</x:v>
       </x:c>
-      <x:c r="F3" s="2" t="str">
+      <x:c r="F3" s="8" t="str">
         <x:v>是否启用</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="3" t="str">
+      <x:c r="A4" s="9" t="str">
         <x:v>Index</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="str">
+      <x:c r="B4" s="9" t="str">
         <x:v>EffectType</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="str">
+      <x:c r="C4" s="9" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="str">
+      <x:c r="D4" s="9" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="str">
+      <x:c r="E4" s="9" t="str">
         <x:v>Note</x:v>
       </x:c>
-      <x:c r="F4" s="3" t="str">
+      <x:c r="F4" s="9" t="str">
         <x:v>Enable</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="1" t="str">
+      <x:c r="A5" s="9" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="str">
+      <x:c r="B5" s="9" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="str">
+      <x:c r="C5" s="9" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="str">
+      <x:c r="D5" s="9" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="str">
+      <x:c r="E5" s="9" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="F5" s="1" t="str">
+      <x:c r="F5" s="9" t="str">
         <x:v>client</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
-      <x:c r="A6" s="1" t="str">
+      <x:c r="A6" s="9" t="str">
         <x:v>uint</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="str">
+      <x:c r="B6" s="9" t="str">
         <x:v>uint</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="str">
+      <x:c r="C6" s="9" t="str">
         <x:v>uint</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="str">
+      <x:c r="D6" s="9" t="str">
         <x:v>float</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="str">
+      <x:c r="E6" s="9" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="F6" s="1" t="str">
+      <x:c r="F6" s="9" t="str">
         <x:v>bool</x:v>
       </x:c>
     </x:row>
@@ -691,6 +711,406 @@
         <x:v>家族树·家族产业·节点3：农田收获产量 +2</x:v>
       </x:c>
       <x:c r="F21" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>乡里互助：利用互助经验整理储藏位置，增加局外仓库格位。</x:v>
+      </x:c>
+      <x:c r="F22" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>物资归整：改进货物分类与入库次序，进一步增加局外仓库格位。</x:v>
+      </x:c>
+      <x:c r="F23" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B24" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C24" t="n">
+        <x:v>2002</x:v>
+      </x:c>
+      <x:c r="D24" t="n">
+        <x:v>-2</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>工役协调：协调材料生产建筑的施工步骤，缩短新建和升级时间。</x:v>
+      </x:c>
+      <x:c r="F24" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B25" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C25" t="n">
+        <x:v>2003</x:v>
+      </x:c>
+      <x:c r="D25" t="n">
+        <x:v>-2</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>匠作联络：借助工匠间的经验往来，缩短图纸生产建筑的施工时间。</x:v>
+      </x:c>
+      <x:c r="F25" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B26" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C26" t="n">
+        <x:v>2002</x:v>
+      </x:c>
+      <x:c r="D26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>材场规制：整理材料生产的作业步骤，增加每个实际工作周期的产出。</x:v>
+      </x:c>
+      <x:c r="F26" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B27" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C27" t="n">
+        <x:v>2003</x:v>
+      </x:c>
+      <x:c r="D27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>工坊熟作：积累工坊经验，增加图纸生产建筑每个工作周期的产出。</x:v>
+      </x:c>
+      <x:c r="F27" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B28" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C28" t="n">
+        <x:v>2004</x:v>
+      </x:c>
+      <x:c r="D28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>市业周转：优化经营作业流程，增加钱财生产建筑每个工作周期的产出。</x:v>
+      </x:c>
+      <x:c r="F28" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B29" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C29" t="n">
+        <x:v>2001</x:v>
+      </x:c>
+      <x:c r="D29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>田事精作：将生产整备经验用于农田，进一步增加每个工作周期的收获。</x:v>
+      </x:c>
+      <x:c r="F29" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B30" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D30" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>起居调养：改善远行前的调养，提高派遣角色生命上限。</x:v>
+      </x:c>
+      <x:c r="F30" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B31" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>体魄训练：持续锻炼体魄，进一步提高派遣角色生命上限。</x:v>
+      </x:c>
+      <x:c r="F31" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B32" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>护行训练：练习行路中的防护动作，减少派遣角色受到的普通伤害。</x:v>
+      </x:c>
+      <x:c r="F32" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>携行整备：归纳门客带回物资的存放方式，增加局外仓库格位。</x:v>
+      </x:c>
+      <x:c r="F33" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B34" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>守备操练：加强基础攻防练习，提高派遣角色普通攻击伤害。</x:v>
+      </x:c>
+      <x:c r="F34" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B35" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D35" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>协防规程：统一协防动作，进一步减少派遣角色受到的普通伤害。</x:v>
+      </x:c>
+      <x:c r="F35" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B36" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D36" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>固守准备：改善守备人员的体魄准备，提高派遣角色生命上限。</x:v>
+      </x:c>
+      <x:c r="F36" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B37" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D37" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>轮值整备：以轮值调养改善远行状态，进一步提高派遣角色生命上限。</x:v>
+      </x:c>
+      <x:c r="F37" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B38" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D38" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>轻装行进：练习行装分配，提高派遣角色水平移动速度。</x:v>
+      </x:c>
+      <x:c r="F38" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B39" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C39" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D39" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>山路适应：通过山路行走锻炼，提高派遣角色生命上限。</x:v>
+      </x:c>
+      <x:c r="F39" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B40" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>临阵配合：练习行动中的攻击配合，提高派遣角色普通攻击伤害。</x:v>
+      </x:c>
+      <x:c r="F40" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D41" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>防护整备：整理远行防护经验，减少派遣角色受到的普通伤害。</x:v>
+      </x:c>
+      <x:c r="F41" s="4" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
